--- a/web/files/九龙-马头角-瑧博.xlsx
+++ b/web/files/九龙-马头角-瑧博.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8310,7 +8310,7 @@
           <t>A | 607呎 (3房)
 $1518万
 $25,015/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -8318,7 +8318,7 @@
           <t>B | 330呎 (2房)
 $927万
 $28,082/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -8326,7 +8326,7 @@
           <t>C | 244呎 (1房)
 $618万
 $25,328/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -8334,7 +8334,7 @@
           <t>D | 335呎 (2房)
 $847万
 $25,281/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -8350,7 +8350,7 @@
           <t>F | 252呎 (1房)
 $400万
 $15,861/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
           <t>A | 607呎 (3房)
 $1233万
 $20,320/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -8373,7 +8373,7 @@
           <t>B | 330呎 (2房)
 $785万
 $23,791/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8381,7 +8381,7 @@
           <t>C | 244呎 (1房)
 $578万
 $23,680/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -8389,7 +8389,7 @@
           <t>D | 335呎 (2房)
 $713万
 $21,281/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -8397,7 +8397,7 @@
           <t>E | 580呎 (3房)
 $1158万
 $19,969/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -8405,7 +8405,7 @@
           <t>F | 252呎 (1房)
 $424万
 $16,825/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8420,7 @@
           <t>A | 607呎 (3房)
 $1358万
 $22,381/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -8428,7 +8428,7 @@
           <t>B | 330呎 (2房)
 $707万
 $21,412/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -8436,7 +8436,7 @@
           <t>C | 244呎 (1房)
 $542万
 $22,213/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -8444,7 +8444,7 @@
           <t>D | 335呎 (2房)
 $701万
 $20,913/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -8452,7 +8452,7 @@
           <t>E | 580呎 (3房)
 $1158万
 $19,967/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -8460,7 +8460,7 @@
           <t>F | 252呎 (1房)
 $399万
 $15,841/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
           <t>A | 607呎 (3房)
 $1301万
 $21,427/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -8483,7 +8483,7 @@
           <t>B | 330呎 (2房)
 $700万
 $21,200/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8491,7 +8491,7 @@
           <t>C | 244呎 (1房)
 $566万
 $23,209/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -8499,7 +8499,7 @@
           <t>D | 335呎 (2房)
 $689万
 $20,555/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -8507,7 +8507,7 @@
           <t>E | 580呎 (3房)
 $1129万
 $19,462/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -8515,7 +8515,7 @@
           <t>F | 252呎 (1房)
 $399万
 $15,833/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
           <t>A | 607呎 (3房)
 $1155万
 $19,025/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -8538,7 +8538,7 @@
           <t>B | 330呎 (2房)
 $762万
 $23,091/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -8546,7 +8546,7 @@
           <t>C | 244呎 (1房)
 $561万
 $22,980/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -8554,7 +8554,7 @@
           <t>D | 335呎 (2房)
 $677万
 $20,203/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -8562,7 +8562,7 @@
           <t>E | 580呎 (3房)
 $1096万
 $18,897/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -8570,7 +8570,7 @@
           <t>F | 252呎 (1房)
 $399万
 $15,825/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
           <t>A | 607呎 (3房)
 $1156万
 $19,041/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -8593,7 +8593,7 @@
           <t>B | 330呎 (2房)
 $686万
 $20,782/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8601,7 +8601,7 @@
           <t>C | 244呎 (1房)
 $504万
 $20,643/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -8609,7 +8609,7 @@
           <t>D | 335呎 (2房)
 $663万
 $19,803/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -8617,7 +8617,7 @@
           <t>E | 580呎 (3房)
 $1080万
 $18,616/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -8625,7 +8625,7 @@
           <t>F | 252呎 (1房)
 $398万
 $15,810/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
           <t>A | 607呎 (3房)
 $1110万
 $18,287/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -8648,7 +8648,7 @@
           <t>B | 330呎 (2房)
 $678万
 $20,536/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -8656,7 +8656,7 @@
           <t>C | 244呎 (1房)
 $548万
 $22,439/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -8664,7 +8664,7 @@
           <t>D | 335呎 (2房)
 $639万
 $19,081/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -8672,7 +8672,7 @@
           <t>E | 580呎 (3房)
 $1034万
 $17,822/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -8680,7 +8680,7 @@
           <t>F | 252呎 (1房)
 $428万
 $16,984/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,7 @@
           <t>A | 607呎 (3房)
 $1155万
 $19,026/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -8703,7 +8703,7 @@
           <t>B | 330呎 (2房)
 $737万
 $22,324/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8711,7 +8711,7 @@
           <t>C | 244呎 (1房)
 $488万
 $20,000/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -8719,7 +8719,7 @@
           <t>D | 335呎 (2房)
 $635万
 $18,949/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -8727,7 +8727,7 @@
           <t>E | 580呎 (3房)
 $1008万
 $17,376/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -8735,7 +8735,7 @@
           <t>F | 252呎 (1房)
 $398万
 $15,778/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
           <t>A | 607呎 (3房)
 $1090万
 $17,951/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -8758,7 +8758,7 @@
           <t>B | 330呎 (2房)
 $722万
 $21,885/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -8766,7 +8766,7 @@
           <t>C | 244呎 (1房)
 $446万
 $18,283/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -8774,7 +8774,7 @@
           <t>D | 335呎 (2房)
 $630万
 $18,818/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -8782,7 +8782,7 @@
           <t>E | 580呎 (3房)
 $996万
 $17,181/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -8790,7 +8790,7 @@
           <t>F | 252呎 (1房)
 $427万
 $16,952/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
           <t>A | 607呎 (3房)
 $1096万
 $18,048/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -8813,7 +8813,7 @@
           <t>B | 330呎 (2房)
 $632万
 $19,167/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8821,7 +8821,7 @@
           <t>C | 244呎 (1房)
 $472万
 $19,336/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -8829,7 +8829,7 @@
           <t>D | 335呎 (2房)
 $626万
 $18,675/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -8837,7 +8837,7 @@
           <t>E | 580呎 (3房)
 $984万
 $16,972/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -8845,7 +8845,7 @@
           <t>F | 252呎 (1房)
 $439万
 $17,437/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
           <t>A | 607呎 (3房)
 $1045万
 $17,216/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -8868,7 +8868,7 @@
           <t>B | 330呎 (2房)
 $635万
 $19,255/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -8876,7 +8876,7 @@
           <t>C | 244呎 (1房)
 $468万
 $19,164/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -8884,7 +8884,7 @@
           <t>D | 335呎 (2房)
 $683万
 $20,388/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -8892,7 +8892,7 @@
           <t>E | 580呎 (3房)
 $990万
 $17,062/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -8900,7 +8900,7 @@
           <t>F | 252呎 (1房)
 $426万
 $16,913/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
           <t>A | 607呎 (3房)
 $1065万
 $17,550/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -8923,7 +8923,7 @@
           <t>B | 330呎 (2房)
 $697万
 $21,118/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8931,7 +8931,7 @@
           <t>C | 244呎 (1房)
 $467万
 $19,131/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -8939,7 +8939,7 @@
           <t>D | 335呎 (2房)
 $618万
 $18,442/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -8947,7 +8947,7 @@
           <t>E | 580呎 (3房)
 $985万
 $16,976/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -8955,7 +8955,7 @@
           <t>F | 252呎 (1房)
 $426万
 $16,897/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
           <t>A | 607呎 (3房)
 $1044万
 $17,199/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -8978,7 +8978,7 @@
           <t>B | 330呎 (2房)
 $695万
 $21,055/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -8986,7 +8986,7 @@
           <t>C | 244呎 (1房)
 $466万
 $19,086/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -8994,7 +8994,7 @@
           <t>D | 335呎 (2房)
 $676万
 $20,185/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -9002,7 +9002,7 @@
           <t>E | 580呎 (3房)
 $980万
 $16,891/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -9010,7 +9010,7 @@
           <t>F | 252呎 (1房)
 $425万
 $16,881/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9025,7 @@
           <t>A | 607呎 (3房)
 $1039万
 $17,114/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -9033,7 +9033,7 @@
           <t>B | 330呎 (2房)
 $630万
 $19,082/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9041,7 +9041,7 @@
           <t>C | 244呎 (1房)
 $511万
 $20,955/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -9049,7 +9049,7 @@
           <t>D | 335呎 (2房)
 $673万
 $20,087/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -9057,7 +9057,7 @@
           <t>E | 580呎 (3房)
 $975万
 $16,807/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -9065,7 +9065,7 @@
           <t>F | 252呎 (1房)
 $425万
 $16,865/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -9080,7 +9080,7 @@
           <t>A | 607呎 (3房)
 $1034万
 $17,028/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -9088,7 +9088,7 @@
           <t>B | 330呎 (2房)
 $691万
 $20,927/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -9096,7 +9096,7 @@
           <t>C | 244呎 (1房)
 $456万
 $18,697/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -9104,7 +9104,7 @@
           <t>D | 335呎 (2房)
 $609万
 $18,167/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -9112,7 +9112,7 @@
           <t>E | 580呎 (3房)
 $970万
 $16,724/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -9120,7 +9120,7 @@
           <t>F | 252呎 (1房)
 $419万
 $16,611/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
           <t>A | 607呎 (3房)
 $1131万
 $18,638/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9143,7 +9143,7 @@
           <t>B | 330呎 (2房)
 $609万
 $18,452/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9151,7 +9151,7 @@
           <t>C | 244呎 (1房)
 $454万
 $18,607/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -9159,7 +9159,7 @@
           <t>D | 335呎 (2房)
 $606万
 $18,078/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -9167,7 +9167,7 @@
           <t>E | 580呎 (3房)
 $962万
 $16,581/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -9175,7 +9175,7 @@
           <t>F | 252呎 (1房)
 $411万
 $16,310/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
           <t>A | 607呎 (3房)
 $1023万
 $16,858/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -9198,7 +9198,7 @@
           <t>B | 330呎 (2房)
 $672万
 $20,348/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -9206,7 +9206,7 @@
           <t>C | 244呎 (1房)
 $452万
 $18,508/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -9214,7 +9214,7 @@
           <t>D | 335呎 (2房)
 $596万
 $17,806/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -9222,7 +9222,7 @@
           <t>E | 580呎 (3房)
 $951万
 $16,400/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -9230,7 +9230,7 @@
           <t>F | 252呎 (1房)
 $444万
 $17,619/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
           <t>A | 607呎 (3房)
 $1013万
 $16,689/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -9253,7 +9253,7 @@
           <t>B | 330呎 (2房)
 $604万
 $18,315/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9261,7 +9261,7 @@
           <t>C | 244呎 (1房)
 $445万
 $18,230/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -9269,7 +9269,7 @@
           <t>D | 335呎 (2房)
 $584万
 $17,448/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -9277,7 +9277,7 @@
           <t>E | 580呎 (3房)
 $1030万
 $17,767/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -9285,7 +9285,7 @@
           <t>F | 252呎 (1房)
 $396万
 $15,730/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
           <t>A | 607呎 (3房)
 $972万
 $16,013/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -9308,7 +9308,7 @@
           <t>B | 330呎 (2房)
 $595万
 $18,036/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -9316,7 +9316,7 @@
           <t>C | 244呎 (1房)
 $438万
 $17,959/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -9324,7 +9324,7 @@
           <t>D | 335呎 (2房)
 $573万
 $17,101/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -9332,7 +9332,7 @@
           <t>E | 580呎 (3房)
 $918万
 $15,829/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -9340,7 +9340,7 @@
           <t>F | 252呎 (1房)
 $388万
 $15,413/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9355,7 @@
           <t>A | 607呎 (3房)
 $954万
 $15,713/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -9363,7 +9363,7 @@
           <t>B | 330呎 (2房)
 $584万
 $17,712/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9371,7 +9371,7 @@
           <t>C | 244呎 (1房)
 $429万
 $17,598/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -9379,7 +9379,7 @@
           <t>D | 335呎 (2房)
 $611万
 $18,248/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -9387,7 +9387,7 @@
           <t>E | 580呎 (3房)
 $900万
 $15,512/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -9395,7 +9395,7 @@
           <t>F | 252呎 (1房)
 $378万
 $14,992/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
